--- a/BOM/solar-glow-drh-v4_0-BOM.xlsx
+++ b/BOM/solar-glow-drh-v4_0-BOM.xlsx
@@ -2547,12 +2547,12 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early. SOURCING: MOUSER only - this is the one non-DigiKey line (e-peas is not a DigiKey vendor); Mouser carries the AEM10300 line (verified 2026-07). Order by MPN 10AEM10300C0000. Mouser live-verified 2026-07-22: 120-AEM10300-QFN (Mouser lists mfr P/N as AEM10300-QFN; the datasheet ordering code 10AEM10300C0000 resolves to this listing), 553 in stock, 16-day lead, $3.77 @1 (breaks 10@$2.81, 25@$2.57, 100@$2.31, 250@$2.19, 1000@$1.85). Schematic U8 symbol now carries Supplier=Mouser + Supplier P/N=120-AEM10300-QFN fields (MPN stays the e-peas ordering code 10AEM10300C0000).</t>
+          <t>Datasheet-confirmed orderable P/N (U8  10AEM10300C0000  $3.77.pdf p1 -- renamed into the refdes convention 2026-08-01, was aem10300.pdf). Specialty long-lead part - order early. SOURCING: MOUSER only - this is the one non-DigiKey line (e-peas is not a DigiKey vendor); Mouser carries the AEM10300 line (verified 2026-07). Order by MPN 10AEM10300C0000. Mouser live-verified 2026-07-22: 120-AEM10300-QFN (Mouser lists mfr P/N as AEM10300-QFN; the datasheet ordering code 10AEM10300C0000 resolves to this listing), 553 in stock, 16-day lead, $3.77 @1 (breaks 10@$2.81, 25@$2.57, 100@$2.31, 250@$2.19, 1000@$1.85). Schematic U8 symbol now carries Supplier=Mouser + Supplier P/N=120-AEM10300-QFN fields (MPN stays the e-peas ordering code 10AEM10300C0000).</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>aem10300.pdf</t>
+          <t>U8  10AEM10300C0000  $3.77.pdf</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>U7  MB85RC512TYPNF-GS-BCERE1  $10.19.pdf</t>
+          <t>U7  MB85RC512TYPN-GS-AWEWE1  $10.19.pdf</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">

--- a/BOM/solar-glow-drh-v4_0-BOM.xlsx
+++ b/BOM/solar-glow-drh-v4_0-BOM.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="L3" s="11" t="inlineStr">
         <is>
-          <t>PV1,PV2  SM141K06TF  $6.98.pdf</t>
+          <t>PV1,PV2  SM141K06TF  $7.61.pdf</t>
         </is>
       </c>
       <c r="M3" s="11" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>SC1-SC4  SCHURTER 3-153-438  $15.48.pdf</t>
+          <t>SC1-SC4  SCHURTER 3-153-438  $16.69.pdf</t>
         </is>
       </c>
       <c r="M4" s="11" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>SC1-SC4  SCHURTER 3-153-438  $15.48.pdf</t>
+          <t>SC1-SC4  SCHURTER 3-153-438  $16.69.pdf</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>U5  NT3H2211W0FHKH  $1.38.pdf</t>
+          <t>U5  NT3H2211W0FHKH  $1.56.pdf</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">

--- a/BOM/solar-glow-drh-v4_0-BOM.xlsx
+++ b/BOM/solar-glow-drh-v4_0-BOM.xlsx
@@ -3010,7 +3010,7 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>Re-pick 2026-07-30 (audit #2). Old GRT188R61A226ME13D (0603/10V X5R) held ~9-12 uF at the 3.1-4.15 V BUFSRC bias vs the AEM10300's min 13 uF (Table 6 footnote 1 names DC-bias derating verbatim). 16V/0805 holds ~15-17 uF. DK 445-7647-1-ND (CT), 11,799 in stock, $0.56 q1, verified live 2026-07-30. Fits in place (measured gaps SC3 0.529 / L2 0.575 / SB2 0.776 mm); a 1206 does NOT fit. LAND: 0603-&gt;0805 sync pending in KiCad (footprint_symbol_mismatch tripwire armed); part_heights 0.90-&gt;1.25 rides with the sync.</t>
+          <t>Re-pick 2026-07-30 (audit #2). Old GRT188R61A226ME13D (0603/10V X5R) held ~9-12 uF at the 3.1-4.15 V BUFSRC bias vs the AEM10300's min 13 uF (Table 6 footnote 1 names DC-bias derating verbatim). 16V/0805 holds ~15-17 uF. DK 445-7647-1-ND (CT), 11,799 in stock, $0.56 q1, verified live 2026-07-30. Fits in place (measured gaps SC3 0.529 / L2 0.575 / SB2 0.776 mm); a 1206 does NOT fit. LAND: 0603-&gt;0805 sync DONE (board carries C_0805_2012Metric; part_heights C25 = 1.25 rode along -- both verified against the committed board, 2026-08-01 sift; this note said "pending" after the sync had landed).</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
